--- a/artfynd/A 26605-2025 artfynd.xlsx
+++ b/artfynd/A 26605-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130107367</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26605-2025 artfynd.xlsx
+++ b/artfynd/A 26605-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130107367</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26605-2025 artfynd.xlsx
+++ b/artfynd/A 26605-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130107367</v>
+        <v>130107329</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507157</v>
+        <v>507152</v>
       </c>
       <c r="R2" t="n">
-        <v>7033174</v>
+        <v>7033148</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Flera fruktkroppar i en levande gran med sockelbildning.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,8 +766,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -774,6 +807,1124 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130107332</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Getsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>507011</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7033080</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130107339</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Getsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>507154</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7032764</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en stående död granhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130107366</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Getsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>507149</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7033155</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130107367</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Getsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>507157</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7033174</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130107372</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Getsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>507223</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7033198</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130107373</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Getsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>507202</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7033195</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran i äldre flersktad granskog.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130108114</v>
+      </c>
+      <c r="B9" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Getsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>507064</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7032974</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130107310</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Getsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>507084</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7033149</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130107328</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Getsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>507190</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7033178</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130107316</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Getsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>507075</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7033179</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26605-2025 artfynd.xlsx
+++ b/artfynd/A 26605-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -807,6 +812,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107329</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107332</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1040,6 +1055,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107339</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1142,6 +1162,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107366</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1244,6 +1269,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107367</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1346,6 +1376,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107372</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1448,6 +1483,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107373</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1564,6 +1604,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108114</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1695,6 +1740,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107310</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1818,6 +1868,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107328</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1925,8 +1980,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107316</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>